--- a/data/POCT_KPI_Database.xlsx
+++ b/data/POCT_KPI_Database.xlsx
@@ -13,6 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="เครื่อง Glucose" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ตัวชี้วัด" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ตัวชี้วัดคุณภาพ (ตั้งค่า)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ผู้ใช้งาน" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="บันทึกการแก้ไข" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'ข้อมูลการใช้งาน'!$A$1:$F$3350</definedName>
@@ -82,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -90,6 +92,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -631,6 +634,46 @@
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>รวมจาก "จำนวนการใช้งาน POCT Glucose ปี งบ 66/67/68/69", "จำนวนการใช้งาน POCT Blood gas ปีงบ 2569", "KPI POCT" — ยอดรวมแถว/คอลัมน์ของไฟล์ต้นฉบับตรวจแล้วตรงทุกไฟล์</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>ผู้ใช้งาน</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Staff ID + PIN (เก็บเป็น hash) ของผู้มีสิทธิ์กรอกข้อมูล — ห้ามพิมพ์ PIN ลงชีตเอง ให้เพิ่มจากเมนู 🔑 POCT หลังบ้าน (SETUP.md ข้อ 4) · ปิดสิทธิ์: ใส่ FALSE ในคอลัมน์ ใช้งาน</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>บันทึกการแก้ไข</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ประวัติการเข้าสู่ระบบและการบันทึกข้อมูลจากหน้าเว็บ (เขียนอัตโนมัติ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>การแชร์ชีต</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>ห้ามแชร์ชีตนี้แบบ "ทุกคนที่มีลิงก์" — เว็บอ่านข้อมูลผ่าน Apps Script แทน (แท็บผู้ใช้งานจะไม่ถูกส่งออกไป)</t>
         </is>
       </c>
     </row>
@@ -94220,4 +94263,118 @@
   <autoFilter ref="A1:M11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>staff_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>ชื่อ-สกุล</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>pin_hash</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>salt</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>ใช้งาน</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>ตั้ง PIN เมื่อ</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>เข้าใช้ล่าสุด</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>เวลา</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Staff ID</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>การกระทำ</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>เดือน</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>ประเภทการตรวจ</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>รายละเอียด</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/POCT_KPI_Database.xlsx
+++ b/data/POCT_KPI_Database.xlsx
@@ -93928,7 +93928,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>มากกว่าร้อยละ 95 ของเครื่องตรวจทั้งหมด</t>
+          <t>มากกว่าร้อยละ 90 ของเครื่องตรวจที่เข้าร่วม (ประเมินเฉพาะเดือนที่มีการทำ EQA — เดือนที่ไม่ได้ทำใส่ ND)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -93943,7 +93943,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -93985,7 +93985,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>มากกว่าร้อยละ 95 ของเครื่องตรวจทั้งหมด</t>
+          <t>มากกว่าร้อยละ 90 ของเครื่องตรวจที่เข้าร่วม (ประเมินเฉพาะเดือนที่มีการทำ EQA — เดือนที่ไม่ได้ทำใส่ ND)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -94004,7 +94004,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>

--- a/data/POCT_KPI_Database.xlsx
+++ b/data/POCT_KPI_Database.xlsx
@@ -93928,7 +93928,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>มากกว่าร้อยละ 90 ของเครื่องตรวจที่เข้าร่วม (ประเมินเฉพาะเดือนที่มีการทำ EQA — เดือนที่ไม่ได้ทำใส่ ND)</t>
+          <t>มากกว่าร้อยละ 95 ของเครื่องตรวจทั้งหมด</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -93943,7 +93943,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr"/>
       <c r="I6" s="2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
@@ -93985,7 +93985,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>มากกว่าร้อยละ 90 ของเครื่องตรวจที่เข้าร่วม (ประเมินเฉพาะเดือนที่มีการทำ EQA — เดือนที่ไม่ได้ทำใส่ ND)</t>
+          <t>มากกว่าร้อยละ 95 ของเครื่องตรวจทั้งหมด</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -94004,7 +94004,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
